--- a/registration_forms/048_music_streaming_service_license_form--registration_forms.xlsx
+++ b/registration_forms/048_music_streaming_service_license_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>license_type1</t>
+          <t>license type1</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>license_type2</t>
+          <t>license type2</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>license_type3</t>
+          <t>license type3</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>streaming_platform1</t>
+          <t>streaming platform1</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>streaming_platform2</t>
+          <t>streaming platform2</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>streaming_platform3</t>
+          <t>streaming platform3</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>streaming_platform4</t>
+          <t>streaming platform4</t>
         </is>
       </c>
     </row>
